--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KRWTNE90HGTG4EG77BZ7BNNB</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTNE90HGTG4EG77BZ7BNNB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
@@ -627,85 +627,85 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRWTP3YS6452424DYYSBB5YA</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTP3YS6452424DYYSBB5YA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRWTPTRGVCW2XW3GH7ER2M6P</t>
+          <t>h_01K421SEM89261VNA9S1Q7KWBV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTPTRGVCW2XW3GH7ER2M6P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K421SEM89261VNA9S1Q7KWBV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRWTQSAJPYQ6RCB6FAYRKP8X</t>
+          <t>h_01KPN3327V11YXB95CHXEXJXBT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSAJPYQ6RCB6FAYRKP8X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPN3327V11YXB95CHXEXJXBT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Account Status Configuration</t>
+          <t>AD Application Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRWTQSAPR8TY78H4DDMW099T</t>
+          <t>h_01KRWTPTRGVCW2XW3GH7ER2M6P</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSAPR8TY78H4DDMW099T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTPTRGVCW2XW3GH7ER2M6P</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Freshservice</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRWTQSARP0JSWMBGTXN16MDE</t>
+          <t>h_01KRX643ZTBZC9VDWMKX1N2109</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSARP0JSWMBGTXN16MDE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRX643ZTBZC9VDWMKX1N2109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KRWTQSASKT2A8VTST34FCAV1</t>
+          <t>h_01KRWTQSAJPYQ6RCB6FAYRKP8X</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSASKT2A8VTST34FCAV1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSAJPYQ6RCB6FAYRKP8X</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Employee Updates</t>
+          <t>Account Status Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRWTQSAZSEGMFEV39H3BZ0E5</t>
+          <t>h_01KRX643ZTDZX7D9FJETP34FVB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSAZSEGMFEV39H3BZ0E5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRX643ZTDZX7D9FJETP34FVB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Freshservice</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
+          <t>h_01KRWTQSARP0JSWMBGTXN16MDE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSARP0JSWMBGTXN16MDE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Name Change</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRWTQSB8E1422QH80RZG4Q8F</t>
+          <t>h_01KRX53A4HNYY45ZEMT7Z90B06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB8E1422QH80RZG4Q8F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRX53A4HNYY45ZEMT7Z90B06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Onboarding Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>User Sync Features</t>
+          <t>Employee Updates</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBEQGF99887SBMBHF73</t>
+          <t>h_01KRWTQSAZSEGMFEV39H3BZ0E5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBEQGF99887SBMBHF73</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSAZSEGMFEV39H3BZ0E5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manage Limit Configuration</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,120 +869,208 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
+          <t>h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Termination Config</t>
+          <t>Name Change</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+          <t>h_01KRWTQSB8E1422QH80RZG4Q8F</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB8E1422QH80RZG4Q8F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Termination Settings</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+          <t>h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>User Sync Features</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>h_01KRWTQSBEQGF99887SBMBHF73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBEQGF99887SBMBHF73</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report-Only Mode Behavior</t>
+          <t>Manage Limit Configuration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Termination Config</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Termination Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Report-Only Mode Behavior</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
         </is>

--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,29 +859,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Employee Updates</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
+          <t>h_01KRXFRSXQGD9FMTYNHBDA3DXB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRXFRSXQGD9FMTYNHBDA3DXB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Name Change</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRWTQSB8E1422QH80RZG4Q8F</t>
+          <t>h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB8E1422QH80RZG4Q8F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB3JSCCQFX9KF94WPRX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Offboarding Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
+          <t>h_01KRXFRSXQ73FS223T8V5KM375</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRXFRSXQ73FS223T8V5KM375</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>User Sync Features</t>
+          <t>Name Change</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBEQGF99887SBMBHF73</t>
+          <t>h_01KRWTQSB8E1422QH80RZG4Q8F</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBEQGF99887SBMBHF73</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSB8E1422QH80RZG4Q8F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Manage Limit Configuration</t>
+          <t>Name Change Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
+          <t>h_01KRXFRSXQCWGRTP2EWHS9S6N0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRXFRSXQCWGRTP2EWHS9S6N0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Termination Config</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+          <t>h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBCZ5072T1J6SGJG0S8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Termination Settings</t>
+          <t>User Sync Features</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+          <t>h_01KRWTQSBEQGF99887SBMBHF73</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBEQGF99887SBMBHF73</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Manage Limit Configuration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBGBGS8TPD6Q9CVYWCG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report-Only Mode Behavior</t>
+          <t>Termination Config</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,32 +1045,98 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBJRWP18HXWBPK8AXP9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Termination Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBKVABV4A4XYP5EAAMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Report-Only Mode Behavior</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
         </is>

--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,66 +1079,506 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBM9Y8YRV9X2STBZ5HE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Report-Only Mode Behavior</t>
+          <t>Dayforce to Active Directory</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>h_01KRZD0PMJA4CAJKM564RM1TMF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBQKPKS95HW4H8SZ7NX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJA4CAJKM564RM1TMF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Location-Based Termination Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KRZBXZ6D65ARR62BT73BGBH6</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZBXZ6D65ARR62BT73BGBH6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dayforce to Freshservice Employee Updates</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KRZCCG5F7J8PD8E08A9KR40T</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZCCG5F7J8PD8E08A9KR40T</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dayforce to Freshservice Name Changes</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJ0SXEFKZTKHWYQ19H</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJ0SXEFKZTKHWYQ19H</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dayforce to Freshservice Offboarding</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJAP0XF9KERTPGXTS0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJAP0XF9KERTPGXTS0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Freshservice to Active Directory Employee Updates</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJ2A9H30HN0RVW2XK6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJ2A9H30HN0RVW2XK6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Freshservice to Active Directory Name Changes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJMBJVSD6EFCXHSG42</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJMBJVSD6EFCXHSG42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJGN6MCQ2Q3DVCXGN1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJGN6MCQ2Q3DVCXGN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KRZD0PMJNGF75S47NXPENH68</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJNGF75S47NXPENH68</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Successful Integration Notification Settings</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Failed Integration Notification Settings</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Skipped Integration Notification Settings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRWTQSBS2P2ZMP9C2QS11DHN</t>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>

--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Termination Config</t>
+          <t>Termination Configuration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1079,161 +1079,161 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Location-Based Termination</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KRXJQ6ZGZE5NSYVXVYMFYVKN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRXJQ6ZGZE5NSYVXVYMFYVKN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dayforce to Active Directory</t>
+          <t>Active Directory Policies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJA4CAJKM564RM1TMF</t>
+          <t>h_01KRZHGQMGE6R3YVYK8NEEX0MR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJA4CAJKM564RM1TMF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHGQMGE6R3YVYK8NEEX0MR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Location-Based Termination Attribute Mapping</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KRZBXZ6D65ARR62BT73BGBH6</t>
+          <t>h_01KRZFAYKKR2BXSP1WK4S0938J</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZBXZ6D65ARR62BT73BGBH6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZFAYKKR2BXSP1WK4S0938J</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dayforce to Freshservice Employee Updates</t>
+          <t>CN Policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KRZCCG5F7J8PD8E08A9KR40T</t>
+          <t>h_01KRZHGQMGW77896QY8B8D4FCZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZCCG5F7J8PD8E08A9KR40T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHGQMGW77896QY8B8D4FCZ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dayforce to Freshservice Name Changes</t>
+          <t>UPN Policy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJ0SXEFKZTKHWYQ19H</t>
+          <t>h_01KRZHGQMGH8E5MX3FRWTH9HT6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJ0SXEFKZTKHWYQ19H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHGQMGH8E5MX3FRWTH9HT6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dayforce to Freshservice Offboarding</t>
+          <t>SAM Account Policy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJAP0XF9KERTPGXTS0</t>
+          <t>h_01KRZHGQMGF6GVD6N00AFH2B2H</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJAP0XF9KERTPGXTS0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHGQMGF6GVD6N00AFH2B2H</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Freshservice to Active Directory Employee Updates</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJ2A9H30HN0RVW2XK6</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJ2A9H30HN0RVW2XK6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Freshservice to Active Directory Name Changes</t>
+          <t>Dayforce to Active Directory</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,85 +1243,85 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJMBJVSD6EFCXHSG42</t>
+          <t>h_01KRZHA54NE5SYTJ15CY22HAKN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJMBJVSD6EFCXHSG42</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NE5SYTJ15CY22HAKN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Location-Based Termination Attribute Mapping</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJGN6MCQ2Q3DVCXGN1</t>
+          <t>h_01KRZBXZ6D65ARR62BT73BGBH6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJGN6MCQ2Q3DVCXGN1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZBXZ6D65ARR62BT73BGBH6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Dayforce to Freshservice Employee Updates</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KRZD0PMJNGF75S47NXPENH68</t>
+          <t>h_01KRZCCG5F7J8PD8E08A9KR40T</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZD0PMJNGF75S47NXPENH68</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZCCG5F7J8PD8E08A9KR40T</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Dayforce to Freshservice Name Changes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KRZHA54NDK0HS6XWV7GC0F18</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NDK0HS6XWV7GC0F18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Dayforce to Freshservice Offboarding</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KRZHA54NEV3ZAJ1P6AVDPEY8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NEV3ZAJ1P6AVDPEY8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Freshservice to Active Directory Employee Updates</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KRZHA54NG3FFB47BP69A2M7Q</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NG3FFB47BP69A2M7Q</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Freshservice to Active Directory Name Changes</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,41 +1375,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KRZHA54N62WPEFSJB06ZQCT4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54N62WPEFSJB06ZQCT4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Rules</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KRZHA54NPDBVQ8YNN7AHYW4A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NPDBVQ8YNN7AHYW4A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>DN Rules</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,41 +1419,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,120 +1463,274 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>User Creation Notification Settings</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KRZS1NK04TK5FJYP68NZQ4W0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZS1NK04TK5FJYP68NZQ4W0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>User Update Notification Settings</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KRZHA54NEREERBQ06T5F5DYV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NEREERBQ06T5F5DYV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>User Termination Notification Settings</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KRZHA54NVN2JYP4GV047QMMR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NVN2JYP4GV047QMMR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Failed Integration Notification Settings</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,68 +1414,68 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KRZRXJ1R2JN44GM05G04XX1E</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZRXJ1R2JN44GM05G04XX1E</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
+          <t>h_01KC6S107RHDBFMTPRRNPNMY70</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KC6S107RHDBFMTPRRNPNMY70</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>User Creation Notification Settings</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,107 +1485,107 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KRZS1NK04TK5FJYP68NZQ4W0</t>
+          <t>h_01KS035E8PFZW2DSY6HQ2H72Q3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZS1NK04TK5FJYP68NZQ4W0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KS035E8PFZW2DSY6HQ2H72Q3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>User Update Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KRZHA54NEREERBQ06T5F5DYV</t>
+          <t>h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NEREERBQ06T5F5DYV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NFKFRT6DBGQJ1VRGB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>User Termination Notification Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>User Creation Notification Settings</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KRZHA54NVN2JYP4GV047QMMR</t>
+          <t>h_01KS01V73N4AR8HBZAZ6CDM6NJ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NVN2JYP4GV047QMMR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KS01V73N4AR8HBZAZ6CDM6NJ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>User Update Notification Settings</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KRZHA54NEREERBQ06T5F5DYV</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NEREERBQ06T5F5DYV</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>User Termination Notification Settings</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1595,19 +1595,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NSC4WCQDYBHH3K8M7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,120 +1617,186 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>h_01KRZHA54NVN2JYP4GV047QMMR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KRZHA54NVN2JYP4GV047QMMR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-Freshservice-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-Freshservice-Integration-Guide/headings.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
